--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9086,0.0273,0.0162,0.0198</t>
-  </si>
-  <si>
-    <t>0.8869,0.0116,0.0053,0.0503</t>
-  </si>
-  <si>
-    <t>0.8164,0.0534,0.0416,0.0602</t>
-  </si>
-  <si>
-    <t>0.9024,0.0260,0.0059,0.0221</t>
-  </si>
-  <si>
-    <t>0.9030,0.0609,0.0150,0.0070</t>
-  </si>
-  <si>
-    <t>0.9272,0.0362,0.0034,0.0054</t>
-  </si>
-  <si>
-    <t>0.7962,0.0905,0.0127,0.0181</t>
-  </si>
-  <si>
-    <t>0.7402,0.0835,0.0158,0.0401</t>
-  </si>
-  <si>
-    <t>0.7511,0.0831,0.0120,0.0336</t>
-  </si>
-  <si>
-    <t>0.7169,0.1743,0.0592,0.0299</t>
-  </si>
-  <si>
-    <t>0.8351,0.0484,0.0142,0.0287</t>
-  </si>
-  <si>
-    <t>0.7619,0.2120,0.0182,0.0074</t>
-  </si>
-  <si>
-    <t>0.9507,0.0080,0.0102,0.0124</t>
-  </si>
-  <si>
-    <t>0.9462,0.0079,0.0140,0.0121</t>
-  </si>
-  <si>
-    <t>0.8251,0.0590,0.0616,0.0405</t>
-  </si>
-  <si>
-    <t>0.6313,0.1205,0.2843,0.0285</t>
-  </si>
-  <si>
-    <t>0.8755,0.0315,0.0493,0.0232</t>
-  </si>
-  <si>
-    <t>0.1928,0.7607,0.0470,0.0089</t>
-  </si>
-  <si>
-    <t>0.7882,0.1726,0.0172,0.0082</t>
-  </si>
-  <si>
-    <t>0.6059,0.3257,0.0499,0.0175</t>
-  </si>
-  <si>
-    <t>0.0347,0.9486,0.0923,0.0059</t>
-  </si>
-  <si>
-    <t>0.0715,0.9429,0.0527,0.0007</t>
-  </si>
-  <si>
-    <t>0.6297,0.2572,0.1268,0.0272</t>
-  </si>
-  <si>
-    <t>0.8995,0.0297,0.0527,0.0130</t>
-  </si>
-  <si>
-    <t>0.9016,0.0113,0.1336,0.0024</t>
-  </si>
-  <si>
-    <t>0.8251,0.0369,0.1403,0.0194</t>
-  </si>
-  <si>
-    <t>0.5227,0.0222,0.6081,0.0080</t>
-  </si>
-  <si>
-    <t>0.8411,0.0193,0.1499,0.0104</t>
-  </si>
-  <si>
-    <t>0.2317,0.0140,0.8738,0.0020</t>
-  </si>
-  <si>
-    <t>0.8556,0.0792,0.0145,0.0113</t>
-  </si>
-  <si>
-    <t>0.6874,0.1520,0.0309,0.0382</t>
-  </si>
-  <si>
-    <t>0.0019,0.8887,0.9781,0.0008</t>
-  </si>
-  <si>
-    <t>0.5665,0.4451,0.0250,0.0106</t>
-  </si>
-  <si>
-    <t>0.8997,0.0299,0.0085,0.0197</t>
-  </si>
-  <si>
-    <t>0.5851,0.2408,0.1213,0.0781</t>
-  </si>
-  <si>
-    <t>0.7583,0.1376,0.0328,0.0190</t>
-  </si>
-  <si>
-    <t>0.4944,0.5499,0.0529,0.0052</t>
-  </si>
-  <si>
-    <t>0.3090,0.4358,0.1557,0.0751</t>
-  </si>
-  <si>
-    <t>0.8116,0.0059,0.2407,0.0047</t>
-  </si>
-  <si>
-    <t>0.7333,0.0072,0.3076,0.0093</t>
-  </si>
-  <si>
-    <t>0.9075,0.0129,0.0609,0.0049</t>
-  </si>
-  <si>
-    <t>0.7209,0.0737,0.2096,0.0111</t>
-  </si>
-  <si>
-    <t>0.1862,0.8374,0.0998,0.0027</t>
-  </si>
-  <si>
-    <t>0.8366,0.0161,0.2410,0.0025</t>
-  </si>
-  <si>
-    <t>0.6094,0.2072,0.0458,0.0711</t>
-  </si>
-  <si>
-    <t>0.5406,0.4826,0.0132,0.0057</t>
-  </si>
-  <si>
-    <t>0.5426,0.5425,0.0374,0.0026</t>
-  </si>
-  <si>
-    <t>0.7151,0.2651,0.0325,0.0084</t>
-  </si>
-  <si>
-    <t>0.3191,0.0376,0.7568,0.0031</t>
-  </si>
-  <si>
-    <t>0.2842,0.4129,0.4237,0.0046</t>
-  </si>
-  <si>
-    <t>0.6055,0.0388,0.4193,0.0141</t>
-  </si>
-  <si>
-    <t>0.7552,0.0616,0.2098,0.0128</t>
-  </si>
-  <si>
-    <t>0.0183,0.1151,0.9832,0.0005</t>
-  </si>
-  <si>
-    <t>0.9289,0.0091,0.0769,0.0027</t>
-  </si>
-  <si>
-    <t>0.8610,0.0521,0.0061,0.0163</t>
-  </si>
-  <si>
-    <t>0.5974,0.2639,0.0677,0.0352</t>
-  </si>
-  <si>
-    <t>0.9050,0.0581,0.0089,0.0082</t>
-  </si>
-  <si>
-    <t>0.0210,0.8843,0.8092,0.0061</t>
-  </si>
-  <si>
-    <t>0.8763,0.0353,0.0119,0.0277</t>
-  </si>
-  <si>
-    <t>0.9278,0.0279,0.0057,0.0098</t>
-  </si>
-  <si>
-    <t>0.8646,0.0794,0.0051,0.0071</t>
-  </si>
-  <si>
-    <t>0.0407,0.8212,0.7442,0.0040</t>
-  </si>
-  <si>
-    <t>0.1884,0.1704,0.7834,0.0112</t>
-  </si>
-  <si>
-    <t>0.4097,0.1513,0.5404,0.0134</t>
-  </si>
-  <si>
-    <t>0.0013,0.9653,0.9499,0.0004</t>
-  </si>
-  <si>
-    <t>0.4383,0.0068,0.7892,0.0012</t>
-  </si>
-  <si>
-    <t>0.3220,0.5468,0.2454,0.0155</t>
-  </si>
-  <si>
-    <t>0.0182,0.9730,0.1417,0.0024</t>
-  </si>
-  <si>
-    <t>0.9368,0.0111,0.0265,0.0136</t>
-  </si>
-  <si>
-    <t>0.8970,0.0422,0.0258,0.0167</t>
-  </si>
-  <si>
-    <t>0.0098,0.6551,0.9617,0.0023</t>
-  </si>
-  <si>
-    <t>0.0582,0.5765,0.8549,0.0033</t>
-  </si>
-  <si>
-    <t>0.5158,0.1399,0.4352,0.0040</t>
-  </si>
-  <si>
-    <t>0.0047,0.9618,0.8285,0.0013</t>
-  </si>
-  <si>
-    <t>0.0409,0.7508,0.8063,0.0076</t>
-  </si>
-  <si>
-    <t>0.5779,0.2464,0.2004,0.0975</t>
-  </si>
-  <si>
-    <t>0.8695,0.0299,0.0090,0.0296</t>
-  </si>
-  <si>
-    <t>0.9593,0.0093,0.0045,0.0100</t>
-  </si>
-  <si>
-    <t>0.5987,0.1417,0.1015,0.1236</t>
-  </si>
-  <si>
-    <t>0.7088,0.1261,0.0947,0.0650</t>
-  </si>
-  <si>
-    <t>0.7066,0.0972,0.0206,0.0568</t>
-  </si>
-  <si>
-    <t>0.1284,0.6444,0.4992,0.0049</t>
-  </si>
-  <si>
-    <t>0.7143,0.0881,0.1767,0.0153</t>
-  </si>
-  <si>
-    <t>0.6936,0.1244,0.1917,0.0055</t>
-  </si>
-  <si>
-    <t>0.0728,0.5310,0.8378,0.0031</t>
-  </si>
-  <si>
-    <t>0.4149,0.3322,0.3463,0.0194</t>
-  </si>
-  <si>
-    <t>0.2318,0.2752,0.7195,0.0046</t>
-  </si>
-  <si>
-    <t>0.7882,0.1700,0.0228,0.0099</t>
-  </si>
-  <si>
-    <t>0.6701,0.3001,0.0201,0.0079</t>
-  </si>
-  <si>
-    <t>0.7113,0.0855,0.0116,0.0407</t>
-  </si>
-  <si>
-    <t>0.8788,0.0731,0.0069,0.0085</t>
-  </si>
-  <si>
-    <t>0.8899,0.0723,0.0101,0.0080</t>
-  </si>
-  <si>
-    <t>0.7676,0.1133,0.0256,0.0306</t>
-  </si>
-  <si>
-    <t>0.8131,0.0946,0.0112,0.0126</t>
-  </si>
-  <si>
-    <t>0.7481,0.1733,0.0231,0.0165</t>
-  </si>
-  <si>
-    <t>0.9088,0.0389,0.0074,0.0122</t>
-  </si>
-  <si>
-    <t>0.8725,0.0288,0.0095,0.0311</t>
-  </si>
-  <si>
-    <t>0.8037,0.1426,0.0151,0.0111</t>
-  </si>
-  <si>
-    <t>0.7586,0.1141,0.0346,0.0414</t>
-  </si>
-  <si>
-    <t>0.8604,0.0488,0.0093,0.0188</t>
-  </si>
-  <si>
-    <t>0.9222,0.0177,0.0027,0.0132</t>
-  </si>
-  <si>
-    <t>0.9288,0.0272,0.0021,0.0059</t>
-  </si>
-  <si>
-    <t>0.7037,0.1728,0.0330,0.0293</t>
-  </si>
-  <si>
-    <t>0.3258,0.0907,0.7557,0.0055</t>
-  </si>
-  <si>
-    <t>0.5473,0.0326,0.5048,0.0155</t>
-  </si>
-  <si>
-    <t>0.9075,0.0192,0.0467,0.0117</t>
-  </si>
-  <si>
-    <t>0.8842,0.0133,0.1054,0.0084</t>
-  </si>
-  <si>
-    <t>0.4247,0.4879,0.0356,0.0206</t>
-  </si>
-  <si>
-    <t>0.1144,0.8659,0.0947,0.0126</t>
-  </si>
-  <si>
-    <t>0.6039,0.1325,0.0406,0.0804</t>
-  </si>
-  <si>
-    <t>0.1065,0.8872,0.0919,0.0030</t>
-  </si>
-  <si>
-    <t>0.0460,0.9305,0.0498,0.0077</t>
-  </si>
-  <si>
-    <t>0.0174,0.9662,0.1051,0.0061</t>
-  </si>
-  <si>
-    <t>0.8529,0.1208,0.0070,0.0060</t>
-  </si>
-  <si>
-    <t>0.8281,0.0683,0.0237,0.0313</t>
-  </si>
-  <si>
-    <t>0.9086,0.0150,0.0534,0.0100</t>
-  </si>
-  <si>
-    <t>0.9322,0.0256,0.0324,0.0053</t>
-  </si>
-  <si>
-    <t>0.9486,0.0084,0.0314,0.0047</t>
-  </si>
-  <si>
-    <t>0.6655,0.2059,0.0747,0.0273</t>
-  </si>
-  <si>
-    <t>0.4709,0.5120,0.0798,0.0080</t>
-  </si>
-  <si>
-    <t>0.1272,0.9182,0.0143,0.0024</t>
-  </si>
-  <si>
-    <t>0.8035,0.0943,0.0467,0.0193</t>
-  </si>
-  <si>
-    <t>0.0295,0.8874,0.7343,0.0067</t>
-  </si>
-  <si>
-    <t>0.8044,0.1661,0.0122,0.0059</t>
-  </si>
-  <si>
-    <t>0.6812,0.2061,0.0182,0.0140</t>
-  </si>
-  <si>
-    <t>0.7271,0.2006,0.0282,0.0158</t>
-  </si>
-  <si>
-    <t>0.8202,0.1026,0.0332,0.0154</t>
-  </si>
-  <si>
-    <t>0.8429,0.0639,0.0068,0.0164</t>
-  </si>
-  <si>
-    <t>0.8499,0.1078,0.0195,0.0113</t>
-  </si>
-  <si>
-    <t>0.8636,0.0560,0.0051,0.0128</t>
-  </si>
-  <si>
-    <t>0.8245,0.0666,0.0135,0.0203</t>
-  </si>
-  <si>
-    <t>0.9408,0.0245,0.0051,0.0088</t>
-  </si>
-  <si>
-    <t>0.7985,0.0875,0.0125,0.0242</t>
-  </si>
-  <si>
-    <t>0.8788,0.0457,0.0067,0.0134</t>
-  </si>
-  <si>
-    <t>0.0423,0.4377,0.9123,0.0016</t>
-  </si>
-  <si>
-    <t>0.9064,0.0412,0.0398,0.0019</t>
-  </si>
-  <si>
-    <t>0.3793,0.0928,0.6521,0.0082</t>
-  </si>
-  <si>
-    <t>0.6727,0.1100,0.2427,0.0133</t>
-  </si>
-  <si>
-    <t>0.7784,0.0867,0.0394,0.0342</t>
-  </si>
-  <si>
-    <t>0.9309,0.0207,0.0058,0.0128</t>
-  </si>
-  <si>
-    <t>0.9530,0.0111,0.0059,0.0078</t>
-  </si>
-  <si>
-    <t>0.9756,0.0044,0.0022,0.0038</t>
-  </si>
-  <si>
-    <t>0.8669,0.0341,0.0170,0.0372</t>
-  </si>
-  <si>
-    <t>0.7735,0.0117,0.0078,0.2362</t>
-  </si>
-  <si>
-    <t>0.8988,0.0170,0.0058,0.0471</t>
-  </si>
-  <si>
-    <t>0.7931,0.0511,0.0519,0.0554</t>
-  </si>
-  <si>
-    <t>0.0232,0.8820,0.5770,0.0296</t>
-  </si>
-  <si>
-    <t>0.8511,0.0453,0.0085,0.0212</t>
-  </si>
-  <si>
-    <t>0.6056,0.3690,0.0508,0.0116</t>
-  </si>
-  <si>
-    <t>0.8140,0.0993,0.0087,0.0142</t>
-  </si>
-  <si>
-    <t>0.6134,0.3285,0.0145,0.0080</t>
-  </si>
-  <si>
-    <t>0.7243,0.1633,0.0282,0.0237</t>
-  </si>
-  <si>
-    <t>0.8032,0.1018,0.0428,0.0248</t>
-  </si>
-  <si>
-    <t>0.9238,0.0474,0.0061,0.0037</t>
-  </si>
-  <si>
-    <t>0.0082,0.8737,0.9325,0.0043</t>
-  </si>
-  <si>
-    <t>0.9578,0.0126,0.0038,0.0060</t>
-  </si>
-  <si>
-    <t>0.9372,0.0292,0.0067,0.0054</t>
-  </si>
-  <si>
-    <t>0.7596,0.1235,0.0382,0.0304</t>
-  </si>
-  <si>
-    <t>0.9035,0.0398,0.0099,0.0126</t>
-  </si>
-  <si>
-    <t>0.8349,0.0999,0.0078,0.0084</t>
-  </si>
-  <si>
-    <t>0.3675,0.5577,0.0420,0.0169</t>
-  </si>
-  <si>
-    <t>0.5604,0.3312,0.0593,0.0271</t>
-  </si>
-  <si>
-    <t>0.7979,0.1921,0.0227,0.0050</t>
-  </si>
-  <si>
-    <t>0.8725,0.0832,0.0088,0.0086</t>
-  </si>
-  <si>
-    <t>0.7304,0.1678,0.0203,0.0204</t>
-  </si>
-  <si>
-    <t>0.6938,0.1644,0.0471,0.0354</t>
-  </si>
-  <si>
-    <t>0.9039,0.0240,0.0052,0.0167</t>
-  </si>
-  <si>
-    <t>0.6282,0.2583,0.0331,0.0240</t>
-  </si>
-  <si>
-    <t>0.8400,0.0333,0.0097,0.0435</t>
-  </si>
-  <si>
-    <t>0.8025,0.0893,0.0177,0.0210</t>
-  </si>
-  <si>
-    <t>0.5821,0.2722,0.0666,0.0414</t>
-  </si>
-  <si>
-    <t>0.4849,0.5402,0.0518,0.0059</t>
-  </si>
-  <si>
-    <t>0.8573,0.1512,0.0066,0.0033</t>
-  </si>
-  <si>
-    <t>0.6075,0.3925,0.0238,0.0053</t>
-  </si>
-  <si>
-    <t>0.6895,0.1101,0.0325,0.0583</t>
-  </si>
-  <si>
-    <t>0.6788,0.3164,0.0356,0.0095</t>
-  </si>
-  <si>
-    <t>0.6693,0.2159,0.0311,0.0258</t>
-  </si>
-  <si>
-    <t>0.7919,0.0848,0.0313,0.0411</t>
-  </si>
-  <si>
-    <t>0.7039,0.3578,0.0221,0.0026</t>
-  </si>
-  <si>
-    <t>0.0091,0.6758,0.9688,0.0012</t>
-  </si>
-  <si>
-    <t>0.8212,0.1738,0.0193,0.0074</t>
-  </si>
-  <si>
-    <t>0.0465,0.0536,0.9735,0.0002</t>
-  </si>
-  <si>
-    <t>0.2854,0.1982,0.6792,0.0140</t>
-  </si>
-  <si>
-    <t>0.2965,0.0989,0.7534,0.0068</t>
-  </si>
-  <si>
-    <t>0.0724,0.4398,0.8441,0.0041</t>
-  </si>
-  <si>
-    <t>0.3057,0.0497,0.7757,0.0046</t>
-  </si>
-  <si>
-    <t>0.2608,0.0655,0.8293,0.0046</t>
-  </si>
-  <si>
-    <t>0.1092,0.0326,0.9353,0.0019</t>
-  </si>
-  <si>
-    <t>0.6937,0.1186,0.2214,0.0332</t>
-  </si>
-  <si>
-    <t>0.9421,0.0096,0.0224,0.0093</t>
-  </si>
-  <si>
-    <t>0.9549,0.0167,0.0057,0.0055</t>
-  </si>
-  <si>
-    <t>0.9101,0.0172,0.0079,0.0228</t>
-  </si>
-  <si>
-    <t>0.8415,0.0696,0.0287,0.0189</t>
-  </si>
-  <si>
-    <t>0.9035,0.0403,0.0278,0.0088</t>
-  </si>
-  <si>
-    <t>0.8115,0.0875,0.0611,0.0322</t>
-  </si>
-  <si>
-    <t>0.7376,0.0723,0.0444,0.0731</t>
-  </si>
-  <si>
-    <t>0.5502,0.3669,0.0584,0.0160</t>
-  </si>
-  <si>
-    <t>0.2108,0.7897,0.1097,0.0093</t>
-  </si>
-  <si>
-    <t>0.7300,0.1846,0.0196,0.0144</t>
-  </si>
-  <si>
-    <t>0.6847,0.2758,0.0203,0.0091</t>
-  </si>
-  <si>
-    <t>0.7758,0.1524,0.0223,0.0176</t>
-  </si>
-  <si>
-    <t>0.9301,0.0178,0.0058,0.0143</t>
-  </si>
-  <si>
-    <t>0.8398,0.0745,0.0292,0.0251</t>
-  </si>
-  <si>
-    <t>0.8492,0.0344,0.1150,0.0118</t>
-  </si>
-  <si>
-    <t>0.9231,0.0186,0.0312,0.0098</t>
-  </si>
-  <si>
-    <t>0.9250,0.0215,0.0298,0.0142</t>
-  </si>
-  <si>
-    <t>0.1738,0.3272,0.7099,0.0087</t>
-  </si>
-  <si>
-    <t>0.6419,0.0724,0.3057,0.0175</t>
-  </si>
-  <si>
-    <t>0.6451,0.0496,0.4012,0.0083</t>
-  </si>
-  <si>
-    <t>0.5821,0.1476,0.2923,0.0105</t>
-  </si>
-  <si>
-    <t>0.1923,0.2341,0.7044,0.0211</t>
-  </si>
-  <si>
-    <t>0.8571,0.0629,0.0115,0.0144</t>
-  </si>
-  <si>
-    <t>0.8960,0.0336,0.0060,0.0157</t>
-  </si>
-  <si>
-    <t>0.8191,0.0332,0.0063,0.0393</t>
-  </si>
-  <si>
-    <t>0.8346,0.0710,0.0137,0.0235</t>
-  </si>
-  <si>
-    <t>0.8877,0.0798,0.0076,0.0055</t>
-  </si>
-  <si>
-    <t>0.7961,0.1143,0.0244,0.0232</t>
-  </si>
-  <si>
-    <t>0.7620,0.0958,0.0114,0.0233</t>
-  </si>
-  <si>
-    <t>0.8433,0.0675,0.0110,0.0180</t>
-  </si>
-  <si>
-    <t>0.7813,0.0970,0.1026,0.0266</t>
-  </si>
-  <si>
-    <t>0.8922,0.0279,0.0096,0.0239</t>
-  </si>
-  <si>
-    <t>0.7158,0.2179,0.0257,0.0150</t>
-  </si>
-  <si>
-    <t>0.0811,0.2285,0.8561,0.0026</t>
-  </si>
-  <si>
-    <t>0.0902,0.2591,0.8741,0.0135</t>
-  </si>
-  <si>
-    <t>0.7133,0.0418,0.3168,0.0164</t>
-  </si>
-  <si>
-    <t>0.1840,0.1492,0.8238,0.0081</t>
-  </si>
-  <si>
-    <t>0.5096,0.2037,0.3450,0.0193</t>
-  </si>
-  <si>
-    <t>0.0092,0.4969,0.9767,0.0013</t>
-  </si>
-  <si>
-    <t>0.6521,0.0173,0.4780,0.0028</t>
-  </si>
-  <si>
-    <t>0.7252,0.1077,0.1319,0.0501</t>
-  </si>
-  <si>
-    <t>0.9293,0.0212,0.0235,0.0139</t>
-  </si>
-  <si>
-    <t>0.8577,0.0505,0.0694,0.0117</t>
-  </si>
-  <si>
-    <t>0.9021,0.0428,0.0246,0.0079</t>
-  </si>
-  <si>
-    <t>0.8010,0.0798,0.0243,0.0330</t>
-  </si>
-  <si>
-    <t>0.8620,0.0457,0.0104,0.0196</t>
-  </si>
-  <si>
-    <t>0.8920,0.0715,0.0067,0.0067</t>
-  </si>
-  <si>
-    <t>0.7608,0.1071,0.0276,0.0349</t>
-  </si>
-  <si>
-    <t>0.8833,0.0447,0.0040,0.0094</t>
-  </si>
-  <si>
-    <t>0.8732,0.0584,0.0062,0.0112</t>
-  </si>
-  <si>
-    <t>0.7740,0.0790,0.0118,0.0297</t>
-  </si>
-  <si>
-    <t>0.8596,0.0972,0.0078,0.0057</t>
-  </si>
-  <si>
-    <t>0.9059,0.0315,0.0396,0.0049</t>
-  </si>
-  <si>
-    <t>0.4756,0.0333,0.6584,0.0025</t>
-  </si>
-  <si>
-    <t>0.3390,0.0612,0.7397,0.0043</t>
-  </si>
-  <si>
-    <t>0.9260,0.0048,0.0672,0.0058</t>
-  </si>
-  <si>
-    <t>0.7662,0.0070,0.4053,0.0015</t>
-  </si>
-  <si>
-    <t>0.8625,0.0462,0.0670,0.0133</t>
-  </si>
-  <si>
-    <t>0.6414,0.1074,0.2875,0.0302</t>
-  </si>
-  <si>
-    <t>0.9033,0.0308,0.0470,0.0082</t>
-  </si>
-  <si>
-    <t>0.9121,0.0436,0.0073,0.0069</t>
-  </si>
-  <si>
-    <t>0.8852,0.0243,0.0255,0.0418</t>
-  </si>
-  <si>
-    <t>0.8612,0.0278,0.0118,0.0579</t>
-  </si>
-  <si>
-    <t>0.7937,0.0230,0.0154,0.1312</t>
-  </si>
-  <si>
-    <t>0.8551,0.0206,0.0139,0.0497</t>
-  </si>
-  <si>
-    <t>0.9422,0.0116,0.0064,0.0131</t>
+    <t>0.9761,0.0068,0.0032,0.0056</t>
+  </si>
+  <si>
+    <t>0.0282,0.0016,0.0012,0.9895</t>
+  </si>
+  <si>
+    <t>0.9789,0.0004,0.0009,0.0227</t>
+  </si>
+  <si>
+    <t>0.2953,0.0229,0.0075,0.7785</t>
+  </si>
+  <si>
+    <t>0.9973,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9952,0.0013,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0021,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9938,0.0016,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9965,0.0008,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.5897,0.0077,0.5987,0.0011</t>
+  </si>
+  <si>
+    <t>0.1617,0.0051,0.9145,0.0024</t>
+  </si>
+  <si>
+    <t>0.6834,0.0052,0.5978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0126,0.0058,0.9886,0.0004</t>
+  </si>
+  <si>
+    <t>0.8772,0.0022,0.2166,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.9945,0.0026,0.0012</t>
+  </si>
+  <si>
+    <t>0.0108,0.9824,0.0009,0.0021</t>
+  </si>
+  <si>
+    <t>0.0033,0.9901,0.0086,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.9978,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.7268,0.0006,0.5182,0.0007</t>
+  </si>
+  <si>
+    <t>0.5472,0.0027,0.6548,0.0024</t>
+  </si>
+  <si>
+    <t>0.0048,0.0013,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.0607,0.0047,0.9631,0.0010</t>
+  </si>
+  <si>
+    <t>0.0740,0.0068,0.9406,0.0023</t>
+  </si>
+  <si>
+    <t>0.4931,0.0011,0.7766,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.0014,0.9959,0.0023</t>
+  </si>
+  <si>
+    <t>0.5367,0.5735,0.0043,0.0006</t>
+  </si>
+  <si>
+    <t>0.4068,0.0829,0.5255,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0048,0.9967,0.0038</t>
+  </si>
+  <si>
+    <t>0.0093,0.9797,0.0087,0.0006</t>
+  </si>
+  <si>
+    <t>0.9567,0.0065,0.0414,0.0017</t>
+  </si>
+  <si>
+    <t>0.0607,0.0095,0.9502,0.0031</t>
+  </si>
+  <si>
+    <t>0.4832,0.5855,0.0287,0.0025</t>
+  </si>
+  <si>
+    <t>0.0067,0.9754,0.4066,0.0014</t>
+  </si>
+  <si>
+    <t>0.0331,0.9141,0.0899,0.0004</t>
+  </si>
+  <si>
+    <t>0.2447,0.0104,0.7476,0.0253</t>
+  </si>
+  <si>
+    <t>0.0035,0.0237,0.9914,0.0025</t>
+  </si>
+  <si>
+    <t>0.2941,0.0068,0.8704,0.0019</t>
+  </si>
+  <si>
+    <t>0.0174,0.1011,0.9724,0.0033</t>
+  </si>
+  <si>
+    <t>0.0131,0.9834,0.0082,0.0001</t>
+  </si>
+  <si>
+    <t>0.0171,0.0036,0.9820,0.0020</t>
+  </si>
+  <si>
+    <t>0.2140,0.1401,0.0267,0.7014</t>
+  </si>
+  <si>
+    <t>0.0047,0.9852,0.0342,0.0058</t>
+  </si>
+  <si>
+    <t>0.0021,0.9844,0.1130,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.9930,0.0126,0.0077</t>
+  </si>
+  <si>
+    <t>0.0037,0.0153,0.9921,0.0023</t>
+  </si>
+  <si>
+    <t>0.0027,0.0131,0.9953,0.0006</t>
+  </si>
+  <si>
+    <t>0.0377,0.0024,0.9840,0.0003</t>
+  </si>
+  <si>
+    <t>0.0043,0.0021,0.9937,0.0010</t>
+  </si>
+  <si>
+    <t>0.0032,0.0016,0.9947,0.0015</t>
+  </si>
+  <si>
+    <t>0.0042,0.2936,0.9791,0.0002</t>
+  </si>
+  <si>
+    <t>0.9788,0.0293,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9885,0.0021,0.0064,0.0013</t>
+  </si>
+  <si>
+    <t>0.9943,0.0024,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.0136,0.9954,0.0054</t>
+  </si>
+  <si>
+    <t>0.9956,0.0015,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9425,0.0712,0.0118,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.9576,0.9565,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0440,0.9933,0.0035</t>
+  </si>
+  <si>
+    <t>0.0037,0.0141,0.9887,0.0035</t>
+  </si>
+  <si>
+    <t>0.0006,0.8832,0.9824,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0775,0.8969,0.0104,0.0013</t>
+  </si>
+  <si>
+    <t>0.0013,0.9957,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.8405,0.0195,0.2474,0.0078</t>
+  </si>
+  <si>
+    <t>0.2943,0.6070,0.2018,0.0315</t>
+  </si>
+  <si>
+    <t>0.0050,0.0070,0.9909,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9726,0.9612,0.0003</t>
+  </si>
+  <si>
+    <t>0.0038,0.4334,0.9667,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9981,0.1668,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9902,0.6640,0.0002</t>
+  </si>
+  <si>
+    <t>0.0983,0.0019,0.0179,0.9207</t>
+  </si>
+  <si>
+    <t>0.0023,0.0064,0.0009,0.9978</t>
+  </si>
+  <si>
+    <t>0.0037,0.0035,0.0012,0.9971</t>
+  </si>
+  <si>
+    <t>0.0086,0.0005,0.0103,0.9887</t>
+  </si>
+  <si>
+    <t>0.0208,0.0024,0.0044,0.9874</t>
+  </si>
+  <si>
+    <t>0.0049,0.0010,0.0008,0.9975</t>
+  </si>
+  <si>
+    <t>0.0011,0.9731,0.7956,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.7228,0.9943,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.9004,0.9701,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.1759,0.9880,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.8799,0.9275,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.7859,0.9521,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9914,0.0052,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9932,0.0059,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9833,0.0018,0.0074,0.0037</t>
+  </si>
+  <si>
+    <t>0.9958,0.0027,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0026,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0018,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9833,0.0161,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9894,0.0024,0.0025,0.0027</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9909,0.0039,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.9945,0.0017,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0390,0.0113,0.9402,0.0318</t>
+  </si>
+  <si>
+    <t>0.0718,0.0281,0.9285,0.0026</t>
+  </si>
+  <si>
+    <t>0.9959,0.0001,0.0063,0.0000</t>
+  </si>
+  <si>
+    <t>0.0360,0.0033,0.9839,0.0002</t>
+  </si>
+  <si>
+    <t>0.0218,0.9775,0.0040,0.0005</t>
+  </si>
+  <si>
+    <t>0.0154,0.9846,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0198,0.9736,0.0047,0.0032</t>
+  </si>
+  <si>
+    <t>0.0046,0.9883,0.0086,0.0018</t>
+  </si>
+  <si>
+    <t>0.0144,0.9855,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9968,0.0059,0.0004</t>
+  </si>
+  <si>
+    <t>0.2007,0.8367,0.0128,0.0042</t>
+  </si>
+  <si>
+    <t>0.2289,0.2178,0.5788,0.0880</t>
+  </si>
+  <si>
+    <t>0.2618,0.0051,0.8316,0.0065</t>
+  </si>
+  <si>
+    <t>0.5708,0.0187,0.5504,0.0047</t>
+  </si>
+  <si>
+    <t>0.3189,0.0148,0.7411,0.0072</t>
+  </si>
+  <si>
+    <t>0.0884,0.2189,0.0633,0.8163</t>
+  </si>
+  <si>
+    <t>0.0030,0.9919,0.0099,0.0012</t>
+  </si>
+  <si>
+    <t>0.0062,0.9900,0.0039,0.0015</t>
+  </si>
+  <si>
+    <t>0.0026,0.9851,0.0163,0.0086</t>
+  </si>
+  <si>
+    <t>0.0012,0.9273,0.9498,0.0005</t>
+  </si>
+  <si>
+    <t>0.0072,0.9928,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.9212,0.0568,0.0242,0.0067</t>
+  </si>
+  <si>
+    <t>0.7726,0.2629,0.0315,0.0066</t>
+  </si>
+  <si>
+    <t>0.9875,0.0040,0.0015,0.0020</t>
+  </si>
+  <si>
+    <t>0.9922,0.0012,0.0044,0.0008</t>
+  </si>
+  <si>
+    <t>0.9954,0.0003,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.9884,0.0032,0.0055,0.0012</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9966,0.0004,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9940,0.0014,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9957,0.0011,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.0051,0.0452,0.9908,0.0002</t>
+  </si>
+  <si>
+    <t>0.0060,0.1606,0.9769,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.1080,0.9867,0.0003</t>
+  </si>
+  <si>
+    <t>0.0272,0.0275,0.9546,0.0018</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.8420,0.0103,0.1950,0.0047</t>
+  </si>
+  <si>
+    <t>0.0477,0.0007,0.9679,0.0023</t>
+  </si>
+  <si>
+    <t>0.8982,0.0047,0.1516,0.0031</t>
+  </si>
+  <si>
+    <t>0.1939,0.0048,0.0138,0.8823</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.0015,0.0349,0.0003,0.9980</t>
+  </si>
+  <si>
+    <t>0.0096,0.0000,0.0004,0.9969</t>
+  </si>
+  <si>
+    <t>0.0029,0.8047,0.8749,0.0112</t>
+  </si>
+  <si>
+    <t>0.9941,0.0015,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.0664,0.9226,0.0018,0.0132</t>
+  </si>
+  <si>
+    <t>0.9935,0.0023,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.1777,0.8537,0.0055,0.0036</t>
+  </si>
+  <si>
+    <t>0.9928,0.0003,0.0015,0.0030</t>
+  </si>
+  <si>
+    <t>0.6980,0.0074,0.0427,0.3282</t>
+  </si>
+  <si>
+    <t>0.9936,0.0015,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.1939,0.9942,0.0054</t>
+  </si>
+  <si>
+    <t>0.9870,0.0009,0.0014,0.0060</t>
+  </si>
+  <si>
+    <t>0.9687,0.0015,0.0043,0.0247</t>
+  </si>
+  <si>
+    <t>0.1533,0.8470,0.0614,0.0131</t>
+  </si>
+  <si>
+    <t>0.9760,0.0077,0.0061,0.0019</t>
+  </si>
+  <si>
+    <t>0.9407,0.0114,0.0466,0.0016</t>
+  </si>
+  <si>
+    <t>0.3012,0.6074,0.1166,0.0061</t>
+  </si>
+  <si>
+    <t>0.5869,0.1655,0.2337,0.0081</t>
+  </si>
+  <si>
+    <t>0.8056,0.2704,0.0078,0.0028</t>
+  </si>
+  <si>
+    <t>0.9928,0.0009,0.0029,0.0018</t>
+  </si>
+  <si>
+    <t>0.9911,0.0008,0.0018,0.0040</t>
+  </si>
+  <si>
+    <t>0.9927,0.0012,0.0027,0.0017</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9961,0.0009,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0026,0.0018,0.0015</t>
+  </si>
+  <si>
+    <t>0.9898,0.0026,0.0042,0.0021</t>
+  </si>
+  <si>
+    <t>0.9797,0.0119,0.0052,0.0020</t>
+  </si>
+  <si>
+    <t>0.8772,0.1337,0.0156,0.0086</t>
+  </si>
+  <si>
+    <t>0.6018,0.5785,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.8433,0.3053,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.8149,0.0541,0.2119,0.0043</t>
+  </si>
+  <si>
+    <t>0.9054,0.1920,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9740,0.0195,0.0034,0.0024</t>
+  </si>
+  <si>
+    <t>0.9900,0.0036,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.9527,0.0426,0.0042,0.0056</t>
+  </si>
+  <si>
+    <t>0.0016,0.0372,0.9964,0.0006</t>
+  </si>
+  <si>
+    <t>0.7197,0.1704,0.1120,0.0063</t>
+  </si>
+  <si>
+    <t>0.0059,0.0145,0.9906,0.0020</t>
+  </si>
+  <si>
+    <t>0.0062,0.0030,0.9915,0.0023</t>
+  </si>
+  <si>
+    <t>0.0222,0.0027,0.9854,0.0005</t>
+  </si>
+  <si>
+    <t>0.0093,0.0112,0.9848,0.0011</t>
+  </si>
+  <si>
+    <t>0.0080,0.0057,0.9917,0.0007</t>
+  </si>
+  <si>
+    <t>0.0093,0.0007,0.9946,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.0023,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.2276,0.0083,0.8742,0.0023</t>
+  </si>
+  <si>
+    <t>0.0438,0.0188,0.9393,0.0183</t>
+  </si>
+  <si>
+    <t>0.7419,0.0614,0.1973,0.0144</t>
+  </si>
+  <si>
+    <t>0.0466,0.0658,0.9125,0.0009</t>
+  </si>
+  <si>
+    <t>0.6272,0.1178,0.1955,0.0024</t>
+  </si>
+  <si>
+    <t>0.3642,0.0428,0.6742,0.0027</t>
+  </si>
+  <si>
+    <t>0.4415,0.0121,0.6588,0.0093</t>
+  </si>
+  <si>
+    <t>0.0397,0.0125,0.9431,0.0012</t>
+  </si>
+  <si>
+    <t>0.0720,0.9280,0.0064,0.0054</t>
+  </si>
+  <si>
+    <t>0.7866,0.3325,0.0040,0.0010</t>
+  </si>
+  <si>
+    <t>0.8807,0.2520,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9608,0.0492,0.0035,0.0017</t>
+  </si>
+  <si>
+    <t>0.4702,0.7192,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.7447,0.0501,0.2142,0.0065</t>
+  </si>
+  <si>
+    <t>0.9879,0.0004,0.0111,0.0007</t>
+  </si>
+  <si>
+    <t>0.9238,0.0069,0.0271,0.0224</t>
+  </si>
+  <si>
+    <t>0.9038,0.0088,0.1312,0.0045</t>
+  </si>
+  <si>
+    <t>0.9907,0.0006,0.0068,0.0004</t>
+  </si>
+  <si>
+    <t>0.0128,0.0085,0.9622,0.0346</t>
+  </si>
+  <si>
+    <t>0.0149,0.1012,0.9352,0.0047</t>
+  </si>
+  <si>
+    <t>0.2960,0.0285,0.8138,0.0040</t>
+  </si>
+  <si>
+    <t>0.1890,0.0192,0.8405,0.0092</t>
+  </si>
+  <si>
+    <t>0.0007,0.0063,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.9954,0.0001,0.0000,0.0040</t>
+  </si>
+  <si>
+    <t>0.9869,0.0116,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.9887,0.0074,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9893,0.0063,0.0025,0.0013</t>
+  </si>
+  <si>
+    <t>0.9941,0.0031,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9964,0.0008,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9896,0.0027,0.0034,0.0019</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.0231,0.0441,0.9666,0.0017</t>
+  </si>
+  <si>
+    <t>0.5593,0.1110,0.4154,0.0108</t>
+  </si>
+  <si>
+    <t>0.7420,0.0016,0.1180,0.0482</t>
+  </si>
+  <si>
+    <t>0.0064,0.0154,0.9906,0.0017</t>
+  </si>
+  <si>
+    <t>0.0061,0.0116,0.9816,0.0171</t>
+  </si>
+  <si>
+    <t>0.0144,0.0425,0.9608,0.0059</t>
+  </si>
+  <si>
+    <t>0.0012,0.0026,0.9970,0.0012</t>
+  </si>
+  <si>
+    <t>0.0145,0.0090,0.9833,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.0015,0.9972,0.0009</t>
+  </si>
+  <si>
+    <t>0.0033,0.0088,0.9943,0.0005</t>
+  </si>
+  <si>
+    <t>0.0128,0.0163,0.9665,0.0023</t>
+  </si>
+  <si>
+    <t>0.9603,0.0033,0.0474,0.0014</t>
+  </si>
+  <si>
+    <t>0.5571,0.0024,0.6202,0.0036</t>
+  </si>
+  <si>
+    <t>0.6080,0.0041,0.0656,0.3028</t>
+  </si>
+  <si>
+    <t>0.9894,0.0057,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9858,0.0131,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.9937,0.0028,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0017,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9963,0.0006,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9916,0.0046,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9959,0.0017,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9913,0.0027,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.0324,0.0074,0.9641,0.0008</t>
+  </si>
+  <si>
+    <t>0.0013,0.0045,0.9965,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.0386,0.9925,0.0053</t>
+  </si>
+  <si>
+    <t>0.0204,0.0071,0.9720,0.0024</t>
+  </si>
+  <si>
+    <t>0.0014,0.0004,0.9963,0.0018</t>
+  </si>
+  <si>
+    <t>0.0206,0.0045,0.9760,0.0023</t>
+  </si>
+  <si>
+    <t>0.0048,0.0014,0.9927,0.0014</t>
+  </si>
+  <si>
+    <t>0.0575,0.2937,0.5279,0.0609</t>
+  </si>
+  <si>
+    <t>0.9824,0.0007,0.0020,0.0122</t>
+  </si>
+  <si>
+    <t>0.0296,0.0033,0.0007,0.9894</t>
+  </si>
+  <si>
+    <t>0.0385,0.0005,0.0011,0.9888</t>
+  </si>
+  <si>
+    <t>0.0035,0.0001,0.0002,0.9988</t>
+  </si>
+  <si>
+    <t>0.0022,0.0004,0.0005,0.9989</t>
+  </si>
+  <si>
+    <t>0.7877,0.0112,0.0321,0.1424</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2121,7 +2121,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>276</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2261,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3549,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
         <v>378</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
